--- a/public/downloads/BukasORR2017.xlsx
+++ b/public/downloads/BukasORR2017.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="56">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,16 +169,37 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>OH</t>
+    <t>Gas shift correction</t>
   </si>
   <si>
-    <t>OOH</t>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>H</t>
   </si>
   <si>
     <t>O2</t>
+  </si>
+  <si>
+    <t>OH</t>
+  </si>
+  <si>
+    <t>OOH</t>
   </si>
 </sst>
 </file>
@@ -662,10 +685,10 @@
         <v>4</v>
       </c>
       <c r="N3" s="5">
-        <v>20.63831925392151</v>
+        <v>20638.31925392151</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03492101396602624</v>
+        <v>34.92101396602624</v>
       </c>
       <c r="P3" s="5">
         <v>591</v>
@@ -696,9 +719,7 @@
       <c r="H4" s="4">
         <v>1.321638693298123</v>
       </c>
-      <c r="I4" s="4">
-        <v>0</v>
-      </c>
+      <c r="I4" s="4"/>
       <c r="J4" s="4">
         <v>1.175369865300036</v>
       </c>
@@ -712,10 +733,10 @@
         <v>4</v>
       </c>
       <c r="N4" s="5">
-        <v>324.4015843868256</v>
+        <v>324401.5843868256</v>
       </c>
       <c r="O4" s="4">
-        <v>0.1240541431689581</v>
+        <v>124.0541431689581</v>
       </c>
       <c r="P4" s="5">
         <v>2615</v>
@@ -762,10 +783,10 @@
         <v>4</v>
       </c>
       <c r="N5" s="5">
-        <v>193.8836438655853</v>
+        <v>193883.6438655853</v>
       </c>
       <c r="O5" s="4">
-        <v>0.4337441697216674</v>
+        <v>433.7441697216674</v>
       </c>
       <c r="P5" s="5">
         <v>447</v>
@@ -812,10 +833,10 @@
         <v>4</v>
       </c>
       <c r="N6" s="5">
-        <v>36.11784410476685</v>
+        <v>36117.84410476685</v>
       </c>
       <c r="O6" s="4">
-        <v>0.1003273447354635</v>
+        <v>100.3273447354635</v>
       </c>
       <c r="P6" s="5">
         <v>360</v>
@@ -862,10 +883,10 @@
         <v>4</v>
       </c>
       <c r="N7" s="5">
-        <v>135.652955532074</v>
+        <v>135652.955532074</v>
       </c>
       <c r="O7" s="4">
-        <v>0.4306443032764253</v>
+        <v>430.6443032764253</v>
       </c>
       <c r="P7" s="5">
         <v>315</v>
@@ -912,10 +933,10 @@
         <v>4</v>
       </c>
       <c r="N8" s="5">
-        <v>10.04522395133972</v>
+        <v>10045.22395133972</v>
       </c>
       <c r="O8" s="4">
-        <v>0.02556036628839624</v>
+        <v>25.56036628839624</v>
       </c>
       <c r="P8" s="5">
         <v>393</v>
@@ -962,10 +983,10 @@
         <v>4</v>
       </c>
       <c r="N9" s="5">
-        <v>19.82502484321594</v>
+        <v>19825.02484321594</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03691810957768332</v>
+        <v>36.91810957768332</v>
       </c>
       <c r="P9" s="5">
         <v>537</v>
@@ -1012,10 +1033,10 @@
         <v>4</v>
       </c>
       <c r="N10" s="5">
-        <v>25.35150718688965</v>
+        <v>25351.50718688965</v>
       </c>
       <c r="O10" s="4">
-        <v>0.09086561715731056</v>
+        <v>90.86561715731057</v>
       </c>
       <c r="P10" s="5">
         <v>279</v>
@@ -1062,10 +1083,10 @@
         <v>4</v>
       </c>
       <c r="N11" s="5">
-        <v>21.52779722213745</v>
+        <v>21527.79722213745</v>
       </c>
       <c r="O11" s="4">
-        <v>0.05996600897531323</v>
+        <v>59.96600897531324</v>
       </c>
       <c r="P11" s="5">
         <v>359</v>
@@ -1096,9 +1117,7 @@
       <c r="H12" s="4">
         <v>0.5999550288933275</v>
       </c>
-      <c r="I12" s="4">
-        <v>0</v>
-      </c>
+      <c r="I12" s="4"/>
       <c r="J12" s="4">
         <v>0.3016525572556017</v>
       </c>
@@ -1112,10 +1131,10 @@
         <v>4</v>
       </c>
       <c r="N12" s="5">
-        <v>16.70908761024475</v>
+        <v>16709.08761024475</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02967866360611856</v>
+        <v>29.67866360611856</v>
       </c>
       <c r="P12" s="5">
         <v>563</v>
@@ -1162,10 +1181,10 @@
         <v>4</v>
       </c>
       <c r="N13" s="5">
-        <v>28.17087864875793</v>
+        <v>28170.87864875793</v>
       </c>
       <c r="O13" s="4">
-        <v>0.08025891352922489</v>
+        <v>80.25891352922488</v>
       </c>
       <c r="P13" s="5">
         <v>351</v>
@@ -1212,10 +1231,10 @@
         <v>4</v>
       </c>
       <c r="N14" s="5">
-        <v>239.2758240699768</v>
+        <v>239275.8240699768</v>
       </c>
       <c r="O14" s="4">
-        <v>0.6135277540255816</v>
+        <v>613.5277540255815</v>
       </c>
       <c r="P14" s="5">
         <v>390</v>
@@ -1262,10 +1281,10 @@
         <v>4</v>
       </c>
       <c r="N15" s="5">
-        <v>174.591475725174</v>
+        <v>174591.475725174</v>
       </c>
       <c r="O15" s="4">
-        <v>0.6062204018235207</v>
+        <v>606.2204018235207</v>
       </c>
       <c r="P15" s="5">
         <v>288</v>
@@ -1312,10 +1331,10 @@
         <v>4</v>
       </c>
       <c r="N16" s="5">
-        <v>44.65501022338867</v>
+        <v>44655.01022338867</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1153876233162498</v>
+        <v>115.3876233162498</v>
       </c>
       <c r="P16" s="5">
         <v>387</v>
@@ -1362,10 +1381,10 @@
         <v>4</v>
       </c>
       <c r="N17" s="5">
-        <v>42.93693614006042</v>
+        <v>42936.93614006042</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1163602605421692</v>
+        <v>116.3602605421692</v>
       </c>
       <c r="P17" s="5">
         <v>369</v>
@@ -1393,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1404,9 +1423,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1440,8 +1465,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1463,25 +1496,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1711712844705143</v>
+        <v>0.7890340754150225</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1711712844705143</v>
+        <v>0.7890340754150225</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1551749140535786</v>
+        <v>0.8884879714205931</v>
       </c>
       <c r="E3" s="4">
-        <v>98.06122448979592</v>
+        <v>95.20408163265306</v>
       </c>
       <c r="F3" s="4">
-        <v>96.91275167785236</v>
+        <v>93.38926174496645</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -1504,25 +1555,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7890340754150225</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7890340754150225</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3233184587408906</v>
+        <v>0.5899014378169936</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3233184587408906</v>
+        <v>0.5899014378169936</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3088818975582091</v>
+        <v>0.6013891906139319</v>
       </c>
       <c r="E4" s="4">
-        <v>98.16326530612245</v>
+        <v>94.38775510204081</v>
       </c>
       <c r="F4" s="4">
-        <v>97.01342281879195</v>
+        <v>92.75167785234899</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -1545,25 +1612,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5899014378169936</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5899014378169936</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2344863775530446</v>
+        <v>0.3271577152946621</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2344863775530446</v>
+        <v>0.3271577152946621</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2673943092987592</v>
+        <v>0.3938738779037164</v>
       </c>
       <c r="E5" s="4">
-        <v>98.36734693877551</v>
+        <v>93.87755102040816</v>
       </c>
       <c r="F5" s="4">
-        <v>97.21476510067114</v>
+        <v>91.30872483221476</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -1586,25 +1669,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3271577152946621</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3271577152946621</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.49454379227672</v>
+        <v>0.4154313930224078</v>
       </c>
       <c r="C6" s="4">
-        <v>0.49454379227672</v>
+        <v>0.4154313930224078</v>
       </c>
       <c r="D6" s="4">
-        <v>0.5253931172689397</v>
+        <v>0.5358153827053855</v>
       </c>
       <c r="E6" s="4">
-        <v>98.36734693877551</v>
+        <v>93.67346938775511</v>
       </c>
       <c r="F6" s="4">
-        <v>97.18120805369128</v>
+        <v>87.48322147651007</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -1627,9 +1726,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.4154313930224078</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.4154313930224078</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1640,6 +1755,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1647,7 +1763,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1658,9 +1774,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1694,8 +1816,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1717,25 +1847,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5544688041224501</v>
+        <v>0.4316403005849414</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5544688041224501</v>
+        <v>0.4316403005849414</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6008221442713759</v>
+        <v>0.6605227853525586</v>
       </c>
       <c r="E3" s="4">
-        <v>97.85714285714286</v>
+        <v>88.46938775510205</v>
       </c>
       <c r="F3" s="4">
-        <v>94.73154362416108</v>
+        <v>87.88590604026845</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -1758,25 +1906,39 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4316403005849414</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4316403005849414</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6406209890756593</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+        <v>0.1566728522193364</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.7679956381235109</v>
+        <v>0.2143815924537114</v>
       </c>
       <c r="E4" s="4">
-        <v>96.83673469387755</v>
+        <v>86.32653061224489</v>
       </c>
       <c r="F4" s="4">
-        <v>75.87248322147651</v>
+        <v>75.03355704697987</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -1799,25 +1961,39 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1566728522193364</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5053867433797412</v>
+        <v>0.8039011294856093</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5053867433797412</v>
+        <v>0.8039011294856093</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5402988527547412</v>
+        <v>0.4959635074152969</v>
       </c>
       <c r="E5" s="4">
-        <v>98.06122448979592</v>
+        <v>86.93877551020408</v>
       </c>
       <c r="F5" s="4">
-        <v>97.34899328859061</v>
+        <v>87.28187919463087</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -1840,25 +2016,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.8039011294856093</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.8039011294856093</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.4972537924659184</v>
+        <v>0.9289303247842775</v>
       </c>
       <c r="C6" s="4">
-        <v>0.4972537924659184</v>
+        <v>0.9289303247842775</v>
       </c>
       <c r="D6" s="4">
-        <v>0.5255073477637699</v>
+        <v>0.7560482447061525</v>
       </c>
       <c r="E6" s="4">
-        <v>97.65306122448979</v>
+        <v>86.53061224489795</v>
       </c>
       <c r="F6" s="4">
-        <v>95.67114093959732</v>
+        <v>85.97315436241611</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -1881,9 +2073,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.9289303247842775</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.9289303247842775</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1894,6 +2102,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1901,7 +2110,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1912,9 +2121,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1948,8 +2163,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1971,173 +2194,255 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5824662978663466</v>
+        <v>0.2344863775530446</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.2344863775530446</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3557791049494766</v>
+        <v>0.2673943092987592</v>
       </c>
       <c r="E3" s="4">
-        <v>92.34693877551021</v>
+        <v>98.36734693877551</v>
       </c>
       <c r="F3" s="4">
-        <v>78.73601789709173</v>
+        <v>97.21476510067114</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2344863775530446</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2344863775530446</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6355040495309816</v>
+        <v>0.49454379227672</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>0.49454379227672</v>
       </c>
       <c r="D4" s="4">
-        <v>0.386495632401465</v>
+        <v>0.5253931172689397</v>
       </c>
       <c r="E4" s="4">
-        <v>92.34693877551021</v>
+        <v>98.36734693877551</v>
       </c>
       <c r="F4" s="4">
-        <v>78.48993288590604</v>
+        <v>97.18120805369128</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
       </c>
       <c r="H4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.49454379227672</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.49454379227672</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6629342172872119</v>
+        <v>0.1711712844705143</v>
       </c>
       <c r="C5" s="4">
-        <v>0</v>
+        <v>0.1711712844705143</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2999989126454883</v>
+        <v>0.1551749140535786</v>
       </c>
       <c r="E5" s="4">
-        <v>93.26530612244898</v>
+        <v>98.06122448979592</v>
       </c>
       <c r="F5" s="4">
-        <v>79.36241610738254</v>
+        <v>96.91275167785236</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
       </c>
       <c r="H5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1711712844705143</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1711712844705143</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.5189155508887699</v>
+        <v>0.3233184587408906</v>
       </c>
       <c r="C6" s="4">
-        <v>0</v>
+        <v>0.3233184587408906</v>
       </c>
       <c r="D6" s="4">
-        <v>0.164336579025977</v>
+        <v>0.3088818975582091</v>
       </c>
       <c r="E6" s="4">
-        <v>92.9251700680272</v>
+        <v>98.16326530612245</v>
       </c>
       <c r="F6" s="4">
-        <v>78.90380313199105</v>
+        <v>97.01342281879195</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
       <c r="H6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3233184587408906</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3233184587408906</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2148,6 +2453,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2155,7 +2461,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2166,9 +2472,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2202,8 +2514,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2225,25 +2545,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2031289870753311</v>
+        <v>0.5053867433797412</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2031289870753311</v>
+        <v>0.5053867433797412</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2918705279841445</v>
+        <v>0.5402988527547412</v>
       </c>
       <c r="E3" s="4">
-        <v>94.18367346938776</v>
+        <v>98.06122448979592</v>
       </c>
       <c r="F3" s="4">
-        <v>94.8993288590604</v>
+        <v>97.34899328859061</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -2266,25 +2604,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5053867433797412</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5053867433797412</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.627499860993384</v>
+        <v>0.4972537924659184</v>
       </c>
       <c r="C4" s="4">
-        <v>0.627499860993384</v>
+        <v>0.4972537924659184</v>
       </c>
       <c r="D4" s="4">
-        <v>0.8163690988931642</v>
+        <v>0.5255073477637699</v>
       </c>
       <c r="E4" s="4">
-        <v>93.36734693877551</v>
+        <v>97.65306122448979</v>
       </c>
       <c r="F4" s="4">
-        <v>81.49888143176733</v>
+        <v>95.67114093959732</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -2307,25 +2661,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4972537924659184</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4972537924659184</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.9194012548197217</v>
+        <v>0.5544688041224501</v>
       </c>
       <c r="C5" s="4">
-        <v>0.9194012548197217</v>
+        <v>0.5544688041224501</v>
       </c>
       <c r="D5" s="4">
-        <v>0.868287410901875</v>
+        <v>0.6008221442713759</v>
       </c>
       <c r="E5" s="4">
-        <v>94.59183673469387</v>
+        <v>97.85714285714286</v>
       </c>
       <c r="F5" s="4">
-        <v>95.23489932885906</v>
+        <v>94.73154362416108</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -2348,34 +2718,48 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5544688041224501</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5544688041224501</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.8872219155418941</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.8872219155418941</v>
-      </c>
+        <v>0.6406209890756593</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>0.8636022637474605</v>
+        <v>0.7679956381235109</v>
       </c>
       <c r="E6" s="4">
-        <v>94.48979591836735</v>
+        <v>96.83673469387755</v>
       </c>
       <c r="F6" s="4">
-        <v>94.79865771812081</v>
+        <v>75.87248322147651</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="5">
         <v>0</v>
@@ -2389,9 +2773,23 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.6406209890756593</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2402,6 +2800,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2409,7 +2808,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2420,9 +2819,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2456,8 +2861,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2479,173 +2892,239 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.07603459906719962</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.07603459906719962</v>
-      </c>
+        <v>0.6629342172872119</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.07955270362042227</v>
+        <v>0.2999989126454883</v>
       </c>
       <c r="E3" s="4">
-        <v>96.63265306122449</v>
+        <v>93.26530612244898</v>
       </c>
       <c r="F3" s="4">
-        <v>94.8993288590604</v>
+        <v>79.36241610738254</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
       </c>
       <c r="H3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6629342172872119</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1746806328211545</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1746806328211545</v>
-      </c>
+        <v>0.5189155508887699</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.1888469879542112</v>
+        <v>0.164336579025977</v>
       </c>
       <c r="E4" s="4">
-        <v>96.32653061224489</v>
+        <v>92.9251700680272</v>
       </c>
       <c r="F4" s="4">
-        <v>94.22818791946308</v>
+        <v>78.90380313199105</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5189155508887699</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.7157053615320492</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.7157053615320492</v>
-      </c>
+        <v>0.5824662978663466</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.7002215053303089</v>
+        <v>0.3557791049494766</v>
       </c>
       <c r="E5" s="4">
-        <v>96.32653061224489</v>
+        <v>92.34693877551021</v>
       </c>
       <c r="F5" s="4">
-        <v>94.83221476510067</v>
+        <v>78.73601789709173</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5824662978663466</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.8462611268150289</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.8462611268150289</v>
-      </c>
+        <v>0.6355040495309816</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>0.8253470490562398</v>
+        <v>0.386495632401465</v>
       </c>
       <c r="E6" s="4">
-        <v>96.22448979591837</v>
+        <v>92.34693877551021</v>
       </c>
       <c r="F6" s="4">
-        <v>94.69798657718121</v>
+        <v>78.48993288590604</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.6355040495309816</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2656,6 +3135,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2663,7 +3143,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2674,9 +3154,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2710,8 +3196,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2733,25 +3227,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3270272378908105</v>
+        <v>0.9194012548197217</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3270272378908105</v>
+        <v>0.9194012548197217</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3325146799071847</v>
+        <v>0.868287410901875</v>
       </c>
       <c r="E3" s="4">
-        <v>99.18367346938776</v>
+        <v>94.59183673469387</v>
       </c>
       <c r="F3" s="4">
-        <v>96.97986577181209</v>
+        <v>95.23489932885906</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -2774,25 +3286,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.9194012548197217</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.9194012548197217</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3648308689680611</v>
+        <v>0.8872219155418941</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3648308689680611</v>
+        <v>0.8872219155418941</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3768598313415672</v>
+        <v>0.8636022637474605</v>
       </c>
       <c r="E4" s="4">
-        <v>99.28571428571429</v>
+        <v>94.48979591836735</v>
       </c>
       <c r="F4" s="4">
-        <v>97.34899328859061</v>
+        <v>94.79865771812081</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -2815,25 +3343,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8872219155418941</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.8872219155418941</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4584062363376484</v>
+        <v>0.2031289870753311</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4584062363376484</v>
+        <v>0.2031289870753311</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4563530053367482</v>
+        <v>0.2918705279841445</v>
       </c>
       <c r="E5" s="4">
-        <v>99.18367346938776</v>
+        <v>94.18367346938776</v>
       </c>
       <c r="F5" s="4">
-        <v>97.58389261744966</v>
+        <v>94.8993288590604</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -2856,25 +3400,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2031289870753311</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2031289870753311</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.9533787797078412</v>
+        <v>0.627499860993384</v>
       </c>
       <c r="C6" s="4">
-        <v>0.9533787797078412</v>
+        <v>0.627499860993384</v>
       </c>
       <c r="D6" s="4">
-        <v>0.9581912587272337</v>
+        <v>0.8163690988931642</v>
       </c>
       <c r="E6" s="4">
-        <v>99.08163265306122</v>
+        <v>93.36734693877551</v>
       </c>
       <c r="F6" s="4">
-        <v>97.48322147651007</v>
+        <v>81.49888143176733</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -2897,9 +3457,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.627499860993384</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.627499860993384</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2910,6 +3486,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2917,7 +3494,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2928,9 +3505,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2964,8 +3547,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2987,25 +3578,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2946603233828429</v>
+        <v>0.7157053615320492</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2946603233828429</v>
+        <v>0.7157053615320492</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2883558357968215</v>
+        <v>0.7002215053303089</v>
       </c>
       <c r="E3" s="4">
-        <v>95.40816326530613</v>
+        <v>96.32653061224489</v>
       </c>
       <c r="F3" s="4">
-        <v>94.06040268456375</v>
+        <v>94.83221476510067</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -3028,25 +3637,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7157053615320492</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7157053615320492</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5316932474289655</v>
+        <v>0.8462611268150289</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5316932474289655</v>
+        <v>0.8462611268150289</v>
       </c>
       <c r="D4" s="4">
-        <v>0.530424383750987</v>
+        <v>0.8253470490562398</v>
       </c>
       <c r="E4" s="4">
-        <v>95.20408163265306</v>
+        <v>96.22448979591837</v>
       </c>
       <c r="F4" s="4">
-        <v>92.81879194630872</v>
+        <v>94.69798657718121</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -3069,25 +3694,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8462611268150289</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.8462611268150289</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3898252512682248</v>
+        <v>0.07603459906719962</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3898252512682248</v>
+        <v>0.07603459906719962</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4115881140697766</v>
+        <v>0.07955270362042227</v>
       </c>
       <c r="E5" s="4">
-        <v>95.40816326530613</v>
+        <v>96.63265306122449</v>
       </c>
       <c r="F5" s="4">
-        <v>93.7248322147651</v>
+        <v>94.8993288590604</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -3110,25 +3751,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.07603459906719962</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07603459906719962</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.5493520329582173</v>
+        <v>0.1746806328211545</v>
       </c>
       <c r="C6" s="4">
-        <v>0.5493520329582173</v>
+        <v>0.1746806328211545</v>
       </c>
       <c r="D6" s="4">
-        <v>0.5623391101949613</v>
+        <v>0.1888469879542112</v>
       </c>
       <c r="E6" s="4">
-        <v>95.51020408163265</v>
+        <v>96.32653061224489</v>
       </c>
       <c r="F6" s="4">
-        <v>93.65771812080537</v>
+        <v>94.22818791946308</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -3151,9 +3808,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1746806328211545</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1746806328211545</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3164,6 +3837,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3171,7 +3845,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3182,9 +3856,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3218,8 +3898,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3241,25 +3929,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.0162533457292609</v>
+        <v>0.4584062363376484</v>
       </c>
       <c r="C3" s="4">
-        <v>0.0162533457292609</v>
+        <v>0.4584062363376484</v>
       </c>
       <c r="D3" s="4">
-        <v>0.001001739026228965</v>
+        <v>0.4563530053367482</v>
       </c>
       <c r="E3" s="4">
-        <v>95.40816326530613</v>
+        <v>99.18367346938776</v>
       </c>
       <c r="F3" s="4">
-        <v>92.91946308724832</v>
+        <v>97.58389261744966</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -3282,25 +3988,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4584062363376484</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4584062363376484</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.09551073359602436</v>
+        <v>0.9533787797078412</v>
       </c>
       <c r="C4" s="4">
-        <v>0.09551073359602436</v>
+        <v>0.9533787797078412</v>
       </c>
       <c r="D4" s="4">
-        <v>0.06718463944525377</v>
+        <v>0.9581912587272337</v>
       </c>
       <c r="E4" s="4">
-        <v>95.71428571428571</v>
+        <v>99.08163265306122</v>
       </c>
       <c r="F4" s="4">
-        <v>93.42281879194631</v>
+        <v>97.48322147651007</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -3323,25 +4045,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9533787797078412</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.9533787797078412</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.226968195604311</v>
+        <v>0.3270272378908105</v>
       </c>
       <c r="C5" s="4">
-        <v>0.226968195604311</v>
+        <v>0.3270272378908105</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2847104634513722</v>
+        <v>0.3325146799071847</v>
       </c>
       <c r="E5" s="4">
-        <v>96.0204081632653</v>
+        <v>99.18367346938776</v>
       </c>
       <c r="F5" s="4">
-        <v>94.36241610738254</v>
+        <v>96.97986577181209</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -3364,25 +4102,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3270272378908105</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3270272378908105</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.7185016701807081</v>
+        <v>0.3648308689680611</v>
       </c>
       <c r="C6" s="4">
-        <v>0.7185016701807081</v>
+        <v>0.3648308689680611</v>
       </c>
       <c r="D6" s="4">
-        <v>0.7811109850992262</v>
+        <v>0.3768598313415672</v>
       </c>
       <c r="E6" s="4">
-        <v>95.91836734693878</v>
+        <v>99.28571428571429</v>
       </c>
       <c r="F6" s="4">
-        <v>93.95973154362416</v>
+        <v>97.34899328859061</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -3405,9 +4159,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3648308689680611</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3648308689680611</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3418,12 +4188,1568 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.3898252512682248</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3898252512682248</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.4115881140697766</v>
+      </c>
+      <c r="E3" s="4">
+        <v>95.40816326530613</v>
+      </c>
+      <c r="F3" s="4">
+        <v>93.7248322147651</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3898252512682248</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3898252512682248</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.5493520329582173</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.5493520329582173</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.5623391101949613</v>
+      </c>
+      <c r="E4" s="4">
+        <v>95.51020408163265</v>
+      </c>
+      <c r="F4" s="4">
+        <v>93.65771812080537</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5493520329582173</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5493520329582173</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.2946603233828429</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.2946603233828429</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.2883558357968215</v>
+      </c>
+      <c r="E5" s="4">
+        <v>95.40816326530613</v>
+      </c>
+      <c r="F5" s="4">
+        <v>94.06040268456375</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2946603233828429</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2946603233828429</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.5316932474289655</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.5316932474289655</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.530424383750987</v>
+      </c>
+      <c r="E6" s="4">
+        <v>95.20408163265306</v>
+      </c>
+      <c r="F6" s="4">
+        <v>92.81879194630872</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.5316932474289655</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.5316932474289655</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.226968195604311</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.226968195604311</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2847104634513722</v>
+      </c>
+      <c r="E3" s="4">
+        <v>96.0204081632653</v>
+      </c>
+      <c r="F3" s="4">
+        <v>94.36241610738254</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.226968195604311</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.226968195604311</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.7185016701807081</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.7185016701807081</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.7811109850992262</v>
+      </c>
+      <c r="E4" s="4">
+        <v>95.91836734693878</v>
+      </c>
+      <c r="F4" s="4">
+        <v>93.95973154362416</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7185016701807081</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.7185016701807081</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.0162533457292609</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.0162533457292609</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.001001739026228965</v>
+      </c>
+      <c r="E5" s="4">
+        <v>95.40816326530613</v>
+      </c>
+      <c r="F5" s="4">
+        <v>92.91946308724832</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.0162533457292609</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.0162533457292609</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.09551073359602436</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.09551073359602436</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.06718463944525377</v>
+      </c>
+      <c r="E6" s="4">
+        <v>95.71428571428571</v>
+      </c>
+      <c r="F6" s="4">
+        <v>93.42281879194631</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.09551073359602436</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.09551073359602436</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>100</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.4647966522824974</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.4647966522824974</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.3690463204038353</v>
+      </c>
+      <c r="K3" s="4">
+        <v>85.79081632653062</v>
+      </c>
+      <c r="L3" s="4">
+        <v>82.01621923937361</v>
+      </c>
+      <c r="M3" s="5">
+        <v>4</v>
+      </c>
+      <c r="N3" s="5">
+        <v>20638.31925392151</v>
+      </c>
+      <c r="O3" s="4">
+        <v>34.92101396602624</v>
+      </c>
+      <c r="P3" s="5">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>100</v>
+      </c>
+      <c r="E4" s="3">
+        <v>100</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1.321638693298123</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4">
+        <v>1.175369865300036</v>
+      </c>
+      <c r="K4" s="4">
+        <v>56.81122448979586</v>
+      </c>
+      <c r="L4" s="4">
+        <v>29.74832214765092</v>
+      </c>
+      <c r="M4" s="5">
+        <v>4</v>
+      </c>
+      <c r="N4" s="5">
+        <v>324401.5843868256</v>
+      </c>
+      <c r="O4" s="4">
+        <v>124.0541431689581</v>
+      </c>
+      <c r="P4" s="5">
+        <v>2615</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>100</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.2597606239414459</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2597606239414459</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.2820973230099922</v>
+      </c>
+      <c r="K5" s="4">
+        <v>94.66836734693878</v>
+      </c>
+      <c r="L5" s="4">
+        <v>91.18288590604027</v>
+      </c>
+      <c r="M5" s="5">
+        <v>4</v>
+      </c>
+      <c r="N5" s="5">
+        <v>193883.6438655853</v>
+      </c>
+      <c r="O5" s="4">
+        <v>433.7441697216674</v>
+      </c>
+      <c r="P5" s="5">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>100</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.6487242048996447</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.6487242048996447</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.6822269028442858</v>
+      </c>
+      <c r="K6" s="4">
+        <v>94.89795918367346</v>
+      </c>
+      <c r="L6" s="4">
+        <v>91.31152125279644</v>
+      </c>
+      <c r="M6" s="5">
+        <v>4</v>
+      </c>
+      <c r="N6" s="5">
+        <v>36117.84410476685</v>
+      </c>
+      <c r="O6" s="4">
+        <v>100.3273447354635</v>
+      </c>
+      <c r="P6" s="5">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>100</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.3293903881258017</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.3293903881258017</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.3323257976717001</v>
+      </c>
+      <c r="K7" s="4">
+        <v>98.44387755102041</v>
+      </c>
+      <c r="L7" s="4">
+        <v>96.40939597315436</v>
+      </c>
+      <c r="M7" s="5">
+        <v>4</v>
+      </c>
+      <c r="N7" s="5">
+        <v>135652.955532074</v>
+      </c>
+      <c r="O7" s="4">
+        <v>430.6443032764253</v>
+      </c>
+      <c r="P7" s="5">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>100</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.5303811553872715</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.5303811553872715</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.6048916056609067</v>
+      </c>
+      <c r="K8" s="4">
+        <v>94.28571428571429</v>
+      </c>
+      <c r="L8" s="4">
+        <v>91.23322147651007</v>
+      </c>
+      <c r="M8" s="5">
+        <v>4</v>
+      </c>
+      <c r="N8" s="5">
+        <v>10045.22395133972</v>
+      </c>
+      <c r="O8" s="4">
+        <v>25.56036628839624</v>
+      </c>
+      <c r="P8" s="5">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>75</v>
+      </c>
+      <c r="C9" s="3">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.5802861517685411</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.7214905849516094</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.5317290324819298</v>
+      </c>
+      <c r="K9" s="4">
+        <v>87.06632653061224</v>
+      </c>
+      <c r="L9" s="4">
+        <v>84.04362416107382</v>
+      </c>
+      <c r="M9" s="5">
+        <v>4</v>
+      </c>
+      <c r="N9" s="5">
+        <v>19825.02484321594</v>
+      </c>
+      <c r="O9" s="4">
+        <v>36.91810957768332</v>
+      </c>
+      <c r="P9" s="5">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>100</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.3058799782602923</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.3058799782602923</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.3142110595448716</v>
+      </c>
+      <c r="K10" s="4">
+        <v>98.23979591836735</v>
+      </c>
+      <c r="L10" s="4">
+        <v>97.08053691275168</v>
+      </c>
+      <c r="M10" s="5">
+        <v>4</v>
+      </c>
+      <c r="N10" s="5">
+        <v>25351.50718688965</v>
+      </c>
+      <c r="O10" s="4">
+        <v>90.86561715731057</v>
+      </c>
+      <c r="P10" s="5">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>75</v>
+      </c>
+      <c r="C11" s="3">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.5494325822609423</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.5190364466560365</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.6086559957283495</v>
+      </c>
+      <c r="K11" s="4">
+        <v>97.60204081632654</v>
+      </c>
+      <c r="L11" s="4">
+        <v>90.90604026845635</v>
+      </c>
+      <c r="M11" s="5">
+        <v>4</v>
+      </c>
+      <c r="N11" s="5">
+        <v>21527.79722213745</v>
+      </c>
+      <c r="O11" s="4">
+        <v>59.96600897531324</v>
+      </c>
+      <c r="P11" s="5">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>100</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.5999550288933275</v>
+      </c>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4">
+        <v>0.3016525572556017</v>
+      </c>
+      <c r="K12" s="4">
+        <v>92.72108843537414</v>
+      </c>
+      <c r="L12" s="4">
+        <v>78.87304250559284</v>
+      </c>
+      <c r="M12" s="5">
+        <v>4</v>
+      </c>
+      <c r="N12" s="5">
+        <v>16709.08761024475</v>
+      </c>
+      <c r="O12" s="4">
+        <v>29.67866360611856</v>
+      </c>
+      <c r="P12" s="5">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>100</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.6593130046075827</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.6593130046075827</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.7100323253816612</v>
+      </c>
+      <c r="K13" s="4">
+        <v>94.15816326530613</v>
+      </c>
+      <c r="L13" s="4">
+        <v>91.60794183445191</v>
+      </c>
+      <c r="M13" s="5">
+        <v>4</v>
+      </c>
+      <c r="N13" s="5">
+        <v>28170.87864875793</v>
+      </c>
+      <c r="O13" s="4">
+        <v>80.25891352922488</v>
+      </c>
+      <c r="P13" s="5">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>100</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.453170430058858</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.453170430058858</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.4484920614902955</v>
+      </c>
+      <c r="K14" s="4">
+        <v>96.37755102040816</v>
+      </c>
+      <c r="L14" s="4">
+        <v>94.66442953020135</v>
+      </c>
+      <c r="M14" s="5">
+        <v>4</v>
+      </c>
+      <c r="N14" s="5">
+        <v>239275.8240699768</v>
+      </c>
+      <c r="O14" s="4">
+        <v>613.5277540255815</v>
+      </c>
+      <c r="P14" s="5">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>100</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.5259107807260903</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.5259107807260903</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.5309796938281834</v>
+      </c>
+      <c r="K15" s="4">
+        <v>99.18367346938776</v>
+      </c>
+      <c r="L15" s="4">
+        <v>97.34899328859061</v>
+      </c>
+      <c r="M15" s="5">
+        <v>4</v>
+      </c>
+      <c r="N15" s="5">
+        <v>174591.475725174</v>
+      </c>
+      <c r="O15" s="4">
+        <v>606.2204018235207</v>
+      </c>
+      <c r="P15" s="5">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>100</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.4413827137595626</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.4413827137595626</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.4481768609531366</v>
+      </c>
+      <c r="K16" s="4">
+        <v>95.38265306122449</v>
+      </c>
+      <c r="L16" s="4">
+        <v>93.56543624161074</v>
+      </c>
+      <c r="M16" s="5">
+        <v>4</v>
+      </c>
+      <c r="N16" s="5">
+        <v>44655.01022338867</v>
+      </c>
+      <c r="O16" s="4">
+        <v>115.3876233162498</v>
+      </c>
+      <c r="P16" s="5">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>100</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.2643084862775761</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.2643084862775761</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.2835019567555203</v>
+      </c>
+      <c r="K17" s="4">
+        <v>95.76530612244898</v>
+      </c>
+      <c r="L17" s="4">
+        <v>93.66610738255034</v>
+      </c>
+      <c r="M17" s="5">
+        <v>4</v>
+      </c>
+      <c r="N17" s="5">
+        <v>42936.93614006042</v>
+      </c>
+      <c r="O17" s="4">
+        <v>116.3602605421692</v>
+      </c>
+      <c r="P17" s="5">
+        <v>369</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3584,13 +5910,13 @@
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
       <c r="N4" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -4178,9 +6504,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4</v>
+      </c>
+      <c r="E4" s="5">
+        <v>4</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4</v>
+      </c>
+      <c r="I4" s="5">
+        <v>3</v>
+      </c>
+      <c r="J4" s="5">
+        <v>3</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>4</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>4</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>3</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>4</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>3</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>4</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>4</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>4</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>4</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>4</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>4</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>4</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4191,9 +7272,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4227,8 +7314,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4250,149 +7345,215 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.06837710397133301</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.06837710397133301</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.579851713346333</v>
+      </c>
+      <c r="E3" s="4">
+        <v>86.73469387755102</v>
+      </c>
+      <c r="F3" s="4">
+        <v>83.12080536912751</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06837710397133301</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06837710397133301</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4338592459571293</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.4338592459571293</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.01012648838876995</v>
+      </c>
+      <c r="E4" s="4">
+        <v>85.91836734693878</v>
+      </c>
+      <c r="F4" s="4">
+        <v>81.9910514541387</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4338592459571293</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4338592459571293</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.4478480155482314</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C5" s="4">
         <v>0.4478480155482314</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D5" s="4">
         <v>0.2055250937953018</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E5" s="4">
         <v>85.30612244897959</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F5" s="4">
         <v>81.81208053691275</v>
       </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4478480155482314</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4478480155482314</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
         <v>0.9091022436532961</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C6" s="4">
         <v>0.9091022436532961</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D6" s="4">
         <v>0.6806819860849367</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E6" s="4">
         <v>85.20408163265306</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F6" s="4">
         <v>81.14093959731544</v>
       </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.06837710397133301</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.06837710397133301</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.579851713346333</v>
-      </c>
-      <c r="E5" s="4">
-        <v>86.73469387755102</v>
-      </c>
-      <c r="F5" s="4">
-        <v>83.12080536912751</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.4338592459571293</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.4338592459571293</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.01012648838876995</v>
-      </c>
-      <c r="E6" s="4">
-        <v>85.91836734693878</v>
-      </c>
-      <c r="F6" s="4">
-        <v>81.9910514541387</v>
-      </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
@@ -4414,9 +7575,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.9091022436532961</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.9091022436532961</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4427,14 +7604,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4445,9 +7623,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4481,8 +7665,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4504,149 +7696,201 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>3.810852375196308</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
+        <v>0.5364710424672656</v>
+      </c>
+      <c r="E3" s="4">
+        <v>47.68707482993203</v>
+      </c>
+      <c r="F3" s="4">
+        <v>19.63087248322148</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>3.810852375196308</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.0127586295020512</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4">
+        <v>1.615895645798438</v>
+      </c>
+      <c r="E4" s="4">
+        <v>56.7006802721089</v>
+      </c>
+      <c r="F4" s="4">
+        <v>29.67561521252794</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.0127586295020512</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.4735209281458877</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
         <v>0.5849375064387343</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E5" s="4">
         <v>63.06122448979592</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F5" s="4">
         <v>36.15212527964206</v>
       </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4735209281458877</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
         <v>0.9894228403482423</v>
       </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
         <v>1.964175266495703</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E6" s="4">
         <v>59.79591836734692</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F6" s="4">
         <v>33.53467561521253</v>
       </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>1</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>3.810852375196308</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.5364710424672656</v>
-      </c>
-      <c r="E5" s="4">
-        <v>47.68707482993203</v>
-      </c>
-      <c r="F5" s="4">
-        <v>19.63087248322148</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.0127586295020512</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1.615895645798438</v>
-      </c>
-      <c r="E6" s="4">
-        <v>56.7006802721089</v>
-      </c>
-      <c r="F6" s="4">
-        <v>29.67561521252794</v>
-      </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
@@ -4668,9 +7912,23 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.9894228403482423</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4681,14 +7939,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4699,9 +7958,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4735,8 +8000,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4758,149 +8031,215 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.2002285982836194</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2002285982836194</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2877493988145299</v>
+      </c>
+      <c r="E3" s="4">
+        <v>94.89795918367346</v>
+      </c>
+      <c r="F3" s="4">
+        <v>91.24161073825503</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2002285982836194</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2002285982836194</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4882896001327106</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.4882896001327106</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.5716138462412426</v>
+      </c>
+      <c r="E4" s="4">
+        <v>94.59183673469387</v>
+      </c>
+      <c r="F4" s="4">
+        <v>90.87248322147651</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4882896001327106</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4882896001327106</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.1462078775181793</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C5" s="4">
         <v>0.1462078775181793</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D5" s="4">
         <v>0.1055830652728103</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E5" s="4">
         <v>94.48979591836735</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F5" s="4">
         <v>91.2751677852349</v>
       </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1462078775181793</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1462078775181793</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
         <v>0.2043164198312746</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C6" s="4">
         <v>0.2043164198312746</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D6" s="4">
         <v>0.1634429817113863</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E6" s="4">
         <v>94.69387755102041</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F6" s="4">
         <v>91.34228187919463</v>
       </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.2002285982836194</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2002285982836194</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.2877493988145299</v>
-      </c>
-      <c r="E5" s="4">
-        <v>94.89795918367346</v>
-      </c>
-      <c r="F5" s="4">
-        <v>91.24161073825503</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.4882896001327106</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.4882896001327106</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.5716138462412426</v>
-      </c>
-      <c r="E6" s="4">
-        <v>94.59183673469387</v>
-      </c>
-      <c r="F6" s="4">
-        <v>90.87248322147651</v>
-      </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
@@ -4922,9 +8261,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2043164198312746</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2043164198312746</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4935,14 +8290,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4953,9 +8309,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4989,8 +8351,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5012,149 +8382,215 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.4060618017446094</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.4060618017446094</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3528367613088184</v>
+      </c>
+      <c r="E3" s="4">
+        <v>95.61224489795919</v>
+      </c>
+      <c r="F3" s="4">
+        <v>95.83892617449665</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4060618017446094</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4060618017446094</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.6718191077125004</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.6718191077125004</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.5665639807593754</v>
+      </c>
+      <c r="E4" s="4">
+        <v>95.61224489795919</v>
+      </c>
+      <c r="F4" s="4">
+        <v>96.00671140939598</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6718191077125004</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6718191077125004</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.6191477115168593</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C5" s="4">
         <v>0.6191477115168593</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D5" s="4">
         <v>0.6952409083857558</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E5" s="4">
         <v>94.79591836734694</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F5" s="4">
         <v>92.81879194630872</v>
       </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6191477115168593</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6191477115168593</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
         <v>0.8978681986246095</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C6" s="4">
         <v>0.8978681986246095</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D6" s="4">
         <v>1.114265960923194</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E6" s="4">
         <v>93.57142857142857</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F6" s="4">
         <v>80.58165548098434</v>
       </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.4060618017446094</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.4060618017446094</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3528367613088184</v>
-      </c>
-      <c r="E5" s="4">
-        <v>95.61224489795919</v>
-      </c>
-      <c r="F5" s="4">
-        <v>95.83892617449665</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.6718191077125004</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.6718191077125004</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.5665639807593754</v>
-      </c>
-      <c r="E6" s="4">
-        <v>95.61224489795919</v>
-      </c>
-      <c r="F6" s="4">
-        <v>96.00671140939598</v>
-      </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
@@ -5176,9 +8612,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.8978681986246095</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.8978681986246095</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5189,14 +8641,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5207,9 +8660,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5243,8 +8702,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5266,149 +8733,215 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.346289005445332</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.346289005445332</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3537581826914258</v>
+      </c>
+      <c r="E3" s="4">
+        <v>98.46938775510205</v>
+      </c>
+      <c r="F3" s="4">
+        <v>96.74496644295301</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.346289005445332</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.346289005445332</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.5107179711449215</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.5107179711449215</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.5155092309105465</v>
+      </c>
+      <c r="E4" s="4">
+        <v>98.60544217687074</v>
+      </c>
+      <c r="F4" s="4">
+        <v>96.87919463087249</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5107179711449215</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5107179711449215</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.115738325835707</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C5" s="4">
         <v>0.115738325835707</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D5" s="4">
         <v>0.1178364093318008</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E5" s="4">
         <v>98.26530612244898</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F5" s="4">
         <v>95.57046979865771</v>
       </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.115738325835707</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.115738325835707</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
         <v>0.3448162500772463</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C6" s="4">
         <v>0.3448162500772463</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D6" s="4">
         <v>0.3421993677530275</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E6" s="4">
         <v>98.43537414965985</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F6" s="4">
         <v>96.44295302013423</v>
       </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.346289005445332</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.346289005445332</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3537581826914258</v>
-      </c>
-      <c r="E5" s="4">
-        <v>98.46938775510205</v>
-      </c>
-      <c r="F5" s="4">
-        <v>96.74496644295301</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.5107179711449215</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.5107179711449215</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.5155092309105465</v>
-      </c>
-      <c r="E6" s="4">
-        <v>98.60544217687074</v>
-      </c>
-      <c r="F6" s="4">
-        <v>96.87919463087249</v>
-      </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
@@ -5430,9 +8963,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3448162500772463</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3448162500772463</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5443,514 +8992,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3271577152946621</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3271577152946621</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.3938738779037164</v>
-      </c>
-      <c r="E3" s="4">
-        <v>93.87755102040816</v>
-      </c>
-      <c r="F3" s="4">
-        <v>91.30872483221476</v>
-      </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.4154313930224078</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.4154313930224078</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.5358153827053855</v>
-      </c>
-      <c r="E4" s="4">
-        <v>93.67346938775511</v>
-      </c>
-      <c r="F4" s="4">
-        <v>87.48322147651007</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.7890340754150225</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.7890340754150225</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.8884879714205931</v>
-      </c>
-      <c r="E5" s="4">
-        <v>95.20408163265306</v>
-      </c>
-      <c r="F5" s="4">
-        <v>93.38926174496645</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.5899014378169936</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.5899014378169936</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.6013891906139319</v>
-      </c>
-      <c r="E6" s="4">
-        <v>94.38775510204081</v>
-      </c>
-      <c r="F6" s="4">
-        <v>92.75167785234899</v>
-      </c>
-      <c r="G6" s="5">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.8039011294856093</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.8039011294856093</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4959635074152969</v>
-      </c>
-      <c r="E3" s="4">
-        <v>86.93877551020408</v>
-      </c>
-      <c r="F3" s="4">
-        <v>87.28187919463087</v>
-      </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.9289303247842775</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.9289303247842775</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.7560482447061525</v>
-      </c>
-      <c r="E4" s="4">
-        <v>86.53061224489795</v>
-      </c>
-      <c r="F4" s="4">
-        <v>85.97315436241611</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.4316403005849414</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.4316403005849414</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.6605227853525586</v>
-      </c>
-      <c r="E5" s="4">
-        <v>88.46938775510205</v>
-      </c>
-      <c r="F5" s="4">
-        <v>87.88590604026845</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.1566728522193364</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.2143815924537114</v>
-      </c>
-      <c r="E6" s="4">
-        <v>86.32653061224489</v>
-      </c>
-      <c r="F6" s="4">
-        <v>75.03355704697987</v>
-      </c>
-      <c r="G6" s="5">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5">
-        <v>1</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
